--- a/history-error-2026-03-31.xlsx
+++ b/history-error-2026-03-31.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -409,11 +409,9 @@
     <col min="8" max="8" width="11.83203125" customWidth="1"/>
     <col min="9" max="9" width="9.83203125" customWidth="1"/>
     <col min="10" max="10" width="23.83203125" customWidth="1"/>
-    <col min="11" max="11" width="23.83203125" customWidth="1"/>
-    <col min="12" max="12" width="9.83203125" customWidth="1"/>
-    <col min="13" max="13" width="8.83203125" customWidth="1"/>
-    <col min="14" max="14" width="23.83203125" customWidth="1"/>
-    <col min="15" max="15" width="19.83203125" customWidth="1"/>
+    <col min="11" max="11" width="9.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,22 +443,22 @@
         <v>scan-by</v>
       </c>
       <c r="J1" t="str">
+        <v>Scanned Code</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Scanner</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Barcode Breakdown</v>
+      </c>
+      <c r="N1" t="str">
         <v>Generated code 1</v>
       </c>
-      <c r="K1" t="str">
+      <c r="O1" t="str">
         <v>Generated code 2</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Scanner</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Scanned Code</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Barcode Breakdown</v>
       </c>
     </row>
     <row r="2">
@@ -468,13 +466,13 @@
         <v>31/03/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>12:12:47</v>
+        <v>12:16:30</v>
       </c>
       <c r="C2" t="str">
         <v>EAD63827619</v>
       </c>
       <c r="D2" t="str">
-        <v>EAD63827619IGA63P0009</v>
+        <v>EAD63827619IGA63P0012</v>
       </c>
       <c r="E2" t="str">
         <v>India</v>
@@ -486,27 +484,21 @@
         <v>2026/03/25</v>
       </c>
       <c r="H2" t="str">
-        <v>0009</v>
+        <v>0012</v>
       </c>
       <c r="I2" t="str">
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>EAD63827619IGA63P0009</v>
+        <v>EAD63827619IGA63P0012</v>
       </c>
       <c r="K2" t="str">
-        <v>EAD63827619IGA63P0009</v>
+        <v/>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>FAIL</v>
       </c>
       <c r="M2" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="N2" t="str">
-        <v>EAD63827619IGA63P0009</v>
-      </c>
-      <c r="O2" t="str">
         <v/>
       </c>
     </row>
@@ -515,36 +507,83 @@
         <v>31/03/2026</v>
       </c>
       <c r="B3" t="str">
+        <v>12:12:47</v>
+      </c>
+      <c r="C3" t="str">
+        <v>EAD63827619</v>
+      </c>
+      <c r="D3" t="str">
+        <v>EAD63827619IGA63P0009</v>
+      </c>
+      <c r="E3" t="str">
+        <v>India</v>
+      </c>
+      <c r="F3" t="str">
+        <v>GA</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026/03/25</v>
+      </c>
+      <c r="H3" t="str">
+        <v>0009</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v>EAD63827619IGA63P0009</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v>EAD63827619IGA63P0009</v>
+      </c>
+      <c r="O3" t="str">
+        <v>EAD63827619IGA63P0009</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="B4" t="str">
         <v>12:06:27</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D4" t="str">
         <v>EAD63827619IGA63P009</v>
       </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
         <v>EAD63827619IGA63P009</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
         <v>EAD63827619IGA63P009</v>
       </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="N3" t="str">
+      <c r="O4" t="str">
         <v>EAD63827619IGA63P009</v>
-      </c>
-      <c r="O3" t="str">
-        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
   </ignoredErrors>
 </worksheet>
 </file>